--- a/기획.xlsx
+++ b/기획.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sang\Documents\GitHub\newrona Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sang\Documents\GitHub\newrona Data\new rona\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C554850-0A3C-4F8F-BB6A-4B843C843222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7100B76D-C66D-4098-ADF3-A0AB5BB1DB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>등급</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,15 +194,123 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기록 어떻게 할것인지 (롤 api 연동?)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>라인별 가중치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>파이어 스토어 연동</t>
+    <t>소환사 이름으로 puuid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이팅 시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록창</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내전창</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보 등록용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비밀 정보 등록용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자창</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체크리스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동 배정 시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>k=10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jisong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키노</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알파카</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필리야</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레몬알</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데스건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모짱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아르엔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -210,7 +318,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,8 +333,17 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,6 +359,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,7 +451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -319,6 +460,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -328,8 +471,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -610,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C4:P15"/>
+  <dimension ref="C4:W34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9" style="1"/>
@@ -620,9 +788,10 @@
     <col min="8" max="8" width="10.625" customWidth="1"/>
     <col min="10" max="10" width="15.625" customWidth="1"/>
     <col min="16" max="16" width="62.375" customWidth="1"/>
+    <col min="19" max="19" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C4" s="2"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -641,11 +810,11 @@
       <c r="L4" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
@@ -664,11 +833,17 @@
       <c r="O5">
         <v>1</v>
       </c>
-      <c r="P5" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -691,11 +866,17 @@
       <c r="O6">
         <v>2</v>
       </c>
-      <c r="P6" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C7" s="2"/>
       <c r="D7" s="3" t="s">
         <v>18</v>
@@ -715,11 +896,17 @@
       <c r="O7">
         <v>3</v>
       </c>
-      <c r="P7" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C8" s="2"/>
       <c r="D8" s="3" t="s">
         <v>19</v>
@@ -736,9 +923,9 @@
       <c r="J8" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C9" s="2"/>
       <c r="D9" s="3" t="s">
         <v>23</v>
@@ -746,7 +933,7 @@
       <c r="E9" s="3">
         <v>160</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G9" t="s">
@@ -755,9 +942,9 @@
       <c r="J9" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P9" s="5"/>
+    </row>
+    <row r="10" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C10" s="2"/>
       <c r="D10" s="3" t="s">
         <v>24</v>
@@ -765,13 +952,13 @@
       <c r="E10" s="3">
         <v>150</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="7"/>
       <c r="J10" t="s">
         <v>9</v>
       </c>
-      <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C11" s="2"/>
       <c r="D11" s="3" t="s">
         <v>25</v>
@@ -779,16 +966,16 @@
       <c r="E11" s="3">
         <v>140</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="8"/>
       <c r="J11" t="s">
         <v>10</v>
       </c>
       <c r="L11" t="s">
         <v>11</v>
       </c>
-      <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C12" s="2"/>
       <c r="D12" s="3" t="s">
         <v>20</v>
@@ -796,7 +983,7 @@
       <c r="E12" s="3">
         <v>130</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="6" t="s">
         <v>32</v>
       </c>
       <c r="J12" t="s">
@@ -808,9 +995,9 @@
       <c r="M12" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C13" s="2"/>
       <c r="D13" s="3" t="s">
         <v>21</v>
@@ -818,9 +1005,9 @@
       <c r="E13" s="3">
         <v>120</v>
       </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C14" s="2"/>
       <c r="D14" s="3" t="s">
         <v>22</v>
@@ -832,7 +1019,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C15" s="2"/>
       <c r="D15" s="3" t="s">
         <v>34</v>
@@ -843,6 +1030,150 @@
       <c r="F15" s="2" t="s">
         <v>35</v>
       </c>
+    </row>
+    <row r="16" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="P16" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="P17" s="11"/>
+    </row>
+    <row r="18" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="P19" s="11"/>
+    </row>
+    <row r="20" spans="9:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P20" s="11"/>
+    </row>
+    <row r="21" spans="9:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P21" s="11"/>
+      <c r="T21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="V21" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="W21" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="9:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="U22" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="V22" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="W22" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="9:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="U23" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="V23" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="W23" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="9:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T24" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="U24" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="V24" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="W24" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="9:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T25" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="U25" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="V25" s="18"/>
+      <c r="W25" s="19"/>
+    </row>
+    <row r="26" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I26" t="s">
+        <v>43</v>
+      </c>
+      <c r="T26" s="12"/>
+      <c r="U26" s="13"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="15"/>
+    </row>
+    <row r="27" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="T27" s="12"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="15"/>
+    </row>
+    <row r="28" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="T28" s="12"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="15"/>
+    </row>
+    <row r="29" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="K29" t="s">
+        <v>53</v>
+      </c>
+      <c r="T29" s="12"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="15"/>
+    </row>
+    <row r="30" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="T30" s="12"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="15"/>
+    </row>
+    <row r="31" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="T31" s="12"/>
+      <c r="U31" s="13"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="15"/>
+    </row>
+    <row r="32" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="T32" s="12"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="15"/>
+    </row>
+    <row r="33" spans="20:23" x14ac:dyDescent="0.3">
+      <c r="T33" s="12"/>
+      <c r="U33" s="13"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="15"/>
+    </row>
+    <row r="34" spans="20:23" x14ac:dyDescent="0.3">
+      <c r="T34" s="12"/>
+      <c r="U34" s="13"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
